--- a/data/trans_dic/P1422-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1422-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,5</t>
+          <t>0,83; 3,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,26</t>
+          <t>0,48; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,44</t>
+          <t>0,34; 3,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,2</t>
+          <t>0,13; 1,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,56</t>
+          <t>0,14; 1,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,08</t>
+          <t>0,78; 2,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,42</t>
+          <t>0,46; 1,63</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,81</t>
+          <t>0,64; 2,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,6</t>
+          <t>0,3; 1,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,99</t>
+          <t>0,63; 1,91</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,79</t>
+          <t>0,63; 2,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,72</t>
+          <t>0,15; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,42</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,36</t>
+          <t>0,4; 3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,58</t>
+          <t>0,59; 3,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,48</t>
+          <t>0,67; 2,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,77</t>
+          <t>0,3; 1,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,83</t>
+          <t>1,48; 3,66</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,79; 2,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,92</t>
+          <t>0,16; 1,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,8</t>
+          <t>0,67; 1,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,35</t>
+          <t>0,26; 1,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,02</t>
+          <t>0,36; 1,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,64</t>
+          <t>0,67; 1,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,75</t>
+          <t>0,13; 0,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,25</t>
+          <t>0,62; 1,35</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,26</t>
+          <t>0,41; 2,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,39</t>
+          <t>0,16; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,28</t>
+          <t>0,54; 2,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,58</t>
+          <t>0,28; 1,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,29; 1,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,66</t>
+          <t>0,76; 1,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,57</t>
+          <t>0,44; 1,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,29</t>
+          <t>0,35; 1,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,62</t>
+          <t>0,78; 1,68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,76</t>
+          <t>0,47; 1,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,17</t>
+          <t>0,11; 1,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,52</t>
+          <t>1,0; 2,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,36</t>
+          <t>0,37; 1,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,06</t>
+          <t>0,15; 0,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,01</t>
+          <t>0,82; 2,06</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,45</t>
+          <t>0,69; 1,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,94</t>
+          <t>0,41; 0,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,64</t>
+          <t>0,96; 1,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,04</t>
+          <t>0,49; 1,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,92</t>
+          <t>0,35; 0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,25</t>
+          <t>0,82; 1,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,09</t>
+          <t>0,63; 1,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,85</t>
+          <t>0,44; 0,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,33</t>
+          <t>0,95; 1,39</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>9059</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 10785</t>
+          <t>0; 12704</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3599; 15025</t>
+          <t>3582; 16108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1948; 11412</t>
+          <t>2634; 13471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5196</t>
+          <t>0; 5241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1200; 11930</t>
+          <t>1196; 12986</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>616; 5363</t>
+          <t>643; 6290</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>948; 11731</t>
+          <t>1074; 12821</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6112; 23881</t>
+          <t>6069; 20988</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3655; 13508</t>
+          <t>4748; 16905</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>10101</t>
         </is>
       </c>
     </row>
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 5113</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7475</t>
+          <t>0; 7545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3347; 12661</t>
+          <t>3068; 13481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1152; 6120</t>
+          <t>1263; 6786</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5207</t>
+          <t>0; 5851</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7548</t>
+          <t>0; 7556</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5479; 16607</t>
+          <t>5708; 17243</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>15167</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3867; 17537</t>
+          <t>3953; 16945</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>782; 8961</t>
+          <t>779; 8423</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3613; 22834</t>
+          <t>6422; 19545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1041; 8752</t>
+          <t>1039; 7941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 8285</t>
+          <t>0; 10081</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>869; 5968</t>
+          <t>1102; 7445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5953; 22078</t>
+          <t>6003; 23374</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2051; 12153</t>
+          <t>2052; 12408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4551; 23575</t>
+          <t>9737; 24066</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>18044</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9762; 27928</t>
+          <t>9188; 26232</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1813; 10541</t>
+          <t>1869; 11622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7185; 18645</t>
+          <t>7634; 19106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1957; 10346</t>
+          <t>1963; 11120</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8371</t>
+          <t>0; 9213</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2232; 9941</t>
+          <t>3088; 10575</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12963; 31616</t>
+          <t>12904; 32443</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2977; 14830</t>
+          <t>2539; 13570</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10852; 25215</t>
+          <t>12447; 26807</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8738</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>16147</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1986; 11541</t>
+          <t>2074; 13255</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>803; 8607</t>
+          <t>982; 8911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3086; 10799</t>
+          <t>3082; 11745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2080; 11983</t>
+          <t>2120; 13125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2148; 12881</t>
+          <t>2165; 12948</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5322; 13875</t>
+          <t>6281; 15664</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5641; 19927</t>
+          <t>5635; 19141</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4713; 17492</t>
+          <t>4724; 17044</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9458; 21275</t>
+          <t>10911; 23406</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>14301</t>
         </is>
       </c>
     </row>
@@ -2459,42 +2459,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5311</t>
+          <t>0; 4790</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5792</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5194; 19512</t>
+          <t>5179; 18731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1086; 12674</t>
+          <t>1198; 13196</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7546; 19161</t>
+          <t>8462; 20963</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5154; 18670</t>
+          <t>5140; 18996</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2021; 14505</t>
+          <t>2121; 13440</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8207; 20156</t>
+          <t>8904; 22238</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>75810</t>
+          <t>82819</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23113; 49499</t>
+          <t>23714; 49400</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13231; 31692</t>
+          <t>13978; 32884</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30298; 55276</t>
+          <t>32850; 59393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16730; 37061</t>
+          <t>17481; 38655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11873; 32349</t>
+          <t>12273; 32926</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25195; 44736</t>
+          <t>29943; 49073</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44967; 76092</t>
+          <t>43643; 76845</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31236; 58653</t>
+          <t>30525; 58937</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62034; 92351</t>
+          <t>67300; 98266</t>
         </is>
       </c>
     </row>
